--- a/tcg/figma.xlsx
+++ b/tcg/figma.xlsx
@@ -146,6 +146,11 @@
           <t xml:space="preserve">Fichier_image</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Image</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr" s="1">
@@ -243,11 +248,16 @@
           <t xml:space="preserve">001.png</t>
         </is>
       </c>
+      <c r="T2" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/001.png</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">001*</t>
+          <t xml:space="preserve">002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="1">
@@ -267,7 +277,7 @@
       </c>
       <c r="E3" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Alternative</t>
+          <t xml:space="preserve">Normale</t>
         </is>
       </c>
       <c r="F3" t="inlineStr" s="1">
@@ -282,7 +292,7 @@
       </c>
       <c r="H3" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Coup de canon</t>
+          <t xml:space="preserve">Salve</t>
         </is>
       </c>
       <c r="I3" t="inlineStr" s="1">
@@ -302,7 +312,7 @@
       </c>
       <c r="L3" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr" s="1">
@@ -317,17 +327,17 @@
       </c>
       <c r="O3" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Enchaînement : +2 si ta carte précédente était une Attaque.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Repeint en doré pour les grandes occasions. Le bruit, lui, n’a pas changé.</t>
+          <t xml:space="preserve">Une salve, puis une autre. Jimmy appelle ça « dire bonjour ».</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Enchaînement</t>
         </is>
       </c>
       <c r="R3" t="inlineStr" s="1">
@@ -337,14 +347,19 @@
       </c>
       <c r="S3" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">001-alt.png</t>
+          <t xml:space="preserve">002.png</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/002.png</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">002</t>
+          <t xml:space="preserve">003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="1">
@@ -369,17 +384,17 @@
       </c>
       <c r="F4" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Commune</t>
+          <t xml:space="preserve">Peu commune</t>
         </is>
       </c>
       <c r="G4" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">●</t>
+          <t xml:space="preserve">✦</t>
         </is>
       </c>
       <c r="H4" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Salve</t>
+          <t xml:space="preserve">Rage de lave</t>
         </is>
       </c>
       <c r="I4" t="inlineStr" s="1">
@@ -399,7 +414,7 @@
       </c>
       <c r="L4" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="M4" t="inlineStr" s="1">
@@ -414,17 +429,17 @@
       </c>
       <c r="O4" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Enchaînement : +2 si ta carte précédente était une Attaque.</t>
+          <t xml:space="preserve">Tu subis 1 dégât.</t>
         </is>
       </c>
       <c r="P4" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Une salve, puis une autre. Jimmy appelle ça « dire bonjour ».</t>
+          <t xml:space="preserve">Attention à la tête… et aux pieds. Surtout aux pieds.</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Enchaînement</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R4" t="inlineStr" s="1">
@@ -434,14 +449,19 @@
       </c>
       <c r="S4" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">002.png</t>
+          <t xml:space="preserve">003.png</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/003.png</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">002*</t>
+          <t xml:space="preserve">004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="1">
@@ -461,22 +481,22 @@
       </c>
       <c r="E5" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Alternative</t>
+          <t xml:space="preserve">Normale</t>
         </is>
       </c>
       <c r="F5" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Commune</t>
+          <t xml:space="preserve">Peu commune</t>
         </is>
       </c>
       <c r="G5" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">●</t>
+          <t xml:space="preserve">✦</t>
         </is>
       </c>
       <c r="H5" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Salve</t>
+          <t xml:space="preserve">Charge du Destroyer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr" s="1">
@@ -496,7 +516,7 @@
       </c>
       <c r="L5" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="M5" t="inlineStr" s="1">
@@ -511,17 +531,17 @@
       </c>
       <c r="O5" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Enchaînement : +2 si ta carte précédente était une Attaque.</t>
+          <t xml:space="preserve">Perforant (ignore le bouclier).</t>
         </is>
       </c>
       <c r="P5" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Jimmy a demandé « une seule salve ». Personne ne l’a écouté.</t>
+          <t xml:space="preserve">Le Destroyer ne frappe pas à la porte. Il passe à travers.</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Enchaînement</t>
+          <t xml:space="preserve">Perforant</t>
         </is>
       </c>
       <c r="R5" t="inlineStr" s="1">
@@ -531,14 +551,19 @@
       </c>
       <c r="S5" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">002-alt.png</t>
+          <t xml:space="preserve">004.png</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/004.png</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">003</t>
+          <t xml:space="preserve">005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="1">
@@ -563,37 +588,37 @@
       </c>
       <c r="F6" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Peu commune</t>
+          <t xml:space="preserve">Commune</t>
         </is>
       </c>
       <c r="G6" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">✦</t>
+          <t xml:space="preserve">●</t>
         </is>
       </c>
       <c r="H6" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Rage de lave</t>
+          <t xml:space="preserve">Surchauffe</t>
         </is>
       </c>
       <c r="I6" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Attaque</t>
+          <t xml:space="preserve">Tactique</t>
         </is>
       </c>
       <c r="J6" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">🗡️</t>
+          <t xml:space="preserve">✨</t>
         </is>
       </c>
       <c r="K6" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#e5484d</t>
+          <t xml:space="preserve">#9b6dff</t>
         </is>
       </c>
       <c r="L6" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M6" t="inlineStr" s="1">
@@ -608,17 +633,17 @@
       </c>
       <c r="O6" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Tu subis 1 dégât.</t>
+          <t xml:space="preserve">Préparation : ta prochaine Attaque fait +3.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Attention à la tête… et aux pieds. Surtout aux pieds.</t>
+          <t xml:space="preserve">Quand le voyant devient rouge, c’est que tout va bien. Enfin, presque.</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Préparation</t>
         </is>
       </c>
       <c r="R6" t="inlineStr" s="1">
@@ -628,14 +653,19 @@
       </c>
       <c r="S6" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">003.png</t>
+          <t xml:space="preserve">005.png</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/005.png</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">003*</t>
+          <t xml:space="preserve">006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="1">
@@ -655,22 +685,22 @@
       </c>
       <c r="E7" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Alternative</t>
+          <t xml:space="preserve">Normale</t>
         </is>
       </c>
       <c r="F7" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Peu commune</t>
+          <t xml:space="preserve">Commune</t>
         </is>
       </c>
       <c r="G7" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">✦</t>
+          <t xml:space="preserve">●</t>
         </is>
       </c>
       <c r="H7" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Rage de lave</t>
+          <t xml:space="preserve">Bombe</t>
         </is>
       </c>
       <c r="I7" t="inlineStr" s="1">
@@ -690,7 +720,7 @@
       </c>
       <c r="L7" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="M7" t="inlineStr" s="1">
@@ -705,17 +735,17 @@
       </c>
       <c r="O7" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Tu subis 1 dégât.</t>
+          <t xml:space="preserve">Si annulée : inflige quand même 2 dégâts.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">On a voulu l’éteindre avec un seau d’eau. On cherche encore le seau.</t>
+          <t xml:space="preserve">Même désamorcée, elle trouve toujours un moyen de faire boum.</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Si annulée</t>
         </is>
       </c>
       <c r="R7" t="inlineStr" s="1">
@@ -725,14 +755,19 @@
       </c>
       <c r="S7" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">003-alt.png</t>
+          <t xml:space="preserve">006.png</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/006.png</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">004</t>
+          <t xml:space="preserve">007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="1">
@@ -757,17 +792,17 @@
       </c>
       <c r="F8" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Peu commune</t>
+          <t xml:space="preserve">Rare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">✦</t>
+          <t xml:space="preserve">✶</t>
         </is>
       </c>
       <c r="H8" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Charge du Destroyer</t>
+          <t xml:space="preserve">Feu de barrage</t>
         </is>
       </c>
       <c r="I8" t="inlineStr" s="1">
@@ -787,7 +822,7 @@
       </c>
       <c r="L8" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="M8" t="inlineStr" s="1">
@@ -802,17 +837,17 @@
       </c>
       <c r="O8" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Perforant (ignore le bouclier).</t>
+          <t xml:space="preserve">Ne peut pas être annulée par un Contre.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Le Destroyer ne frappe pas à la porte. Il passe à travers.</t>
+          <t xml:space="preserve">Contrer ça ? Bonne chance. Il y en a partout.</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Perforant</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R8" t="inlineStr" s="1">
@@ -822,14 +857,19 @@
       </c>
       <c r="S8" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">004.png</t>
+          <t xml:space="preserve">007.png</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/007.png</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">004*</t>
+          <t xml:space="preserve">008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="1">
@@ -849,22 +889,22 @@
       </c>
       <c r="E9" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Alternative</t>
+          <t xml:space="preserve">Normale</t>
         </is>
       </c>
       <c r="F9" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Peu commune</t>
+          <t xml:space="preserve">Rare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">✦</t>
+          <t xml:space="preserve">✶</t>
         </is>
       </c>
       <c r="H9" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Charge du Destroyer</t>
+          <t xml:space="preserve">Furie</t>
         </is>
       </c>
       <c r="I9" t="inlineStr" s="1">
@@ -884,7 +924,7 @@
       </c>
       <c r="L9" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="M9" t="inlineStr" s="1">
@@ -899,17 +939,17 @@
       </c>
       <c r="O9" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Perforant (ignore le bouclier).</t>
+          <t xml:space="preserve">X = nombre de tes Attaques déjà révélées ce tour (6 au plus).</t>
         </is>
       </c>
       <c r="P9" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Version collector : même trou dans le mur, en plus brillant.</t>
+          <t xml:space="preserve">Plus on la provoque, plus elle cogne fort.</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Perforant</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R9" t="inlineStr" s="1">
@@ -919,14 +959,19 @@
       </c>
       <c r="S9" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">004-alt.png</t>
+          <t xml:space="preserve">008.png</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/008.png</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">005</t>
+          <t xml:space="preserve">009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="1">
@@ -961,22 +1006,22 @@
       </c>
       <c r="H10" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Surchauffe</t>
+          <t xml:space="preserve">Parade glacée</t>
         </is>
       </c>
       <c r="I10" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Tactique</t>
+          <t xml:space="preserve">Contre</t>
         </is>
       </c>
       <c r="J10" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">✨</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="K10" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#9b6dff</t>
+          <t xml:space="preserve">#22b8cf</t>
         </is>
       </c>
       <c r="L10" t="inlineStr" s="1">
@@ -986,27 +1031,27 @@
       </c>
       <c r="M10" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Rouge</t>
+          <t xml:space="preserve">Bleu</t>
         </is>
       </c>
       <c r="N10" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#e2483d</t>
+          <t xml:space="preserve">#3fa9f5</t>
         </is>
       </c>
       <c r="O10" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Préparation : ta prochaine Attaque fait +3.</t>
+          <t xml:space="preserve">Annule une Attaque.</t>
         </is>
       </c>
       <c r="P10" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Quand le voyant devient rouge, c’est que tout va bien. Enfin, presque.</t>
+          <t xml:space="preserve">Un pas de côté, un peu de givre, et l’attaque glisse.</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Préparation</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R10" t="inlineStr" s="1">
@@ -1016,14 +1061,19 @@
       </c>
       <c r="S10" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">005.png</t>
+          <t xml:space="preserve">009.png</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/009.png</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">005*</t>
+          <t xml:space="preserve">010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="1">
@@ -1043,37 +1093,37 @@
       </c>
       <c r="E11" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Alternative</t>
+          <t xml:space="preserve">Normale</t>
         </is>
       </c>
       <c r="F11" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Commune</t>
+          <t xml:space="preserve">Rare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">●</t>
+          <t xml:space="preserve">✶</t>
         </is>
       </c>
       <c r="H11" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Surchauffe</t>
+          <t xml:space="preserve">Miroir de glace</t>
         </is>
       </c>
       <c r="I11" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Tactique</t>
+          <t xml:space="preserve">Contre</t>
         </is>
       </c>
       <c r="J11" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">✨</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="K11" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#9b6dff</t>
+          <t xml:space="preserve">#22b8cf</t>
         </is>
       </c>
       <c r="L11" t="inlineStr" s="1">
@@ -1083,27 +1133,27 @@
       </c>
       <c r="M11" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Rouge</t>
+          <t xml:space="preserve">Bleu</t>
         </is>
       </c>
       <c r="N11" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#e2483d</t>
+          <t xml:space="preserve">#3fa9f5</t>
         </is>
       </c>
       <c r="O11" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Préparation : ta prochaine Attaque fait +3.</t>
+          <t xml:space="preserve">Annule une Attaque et renvoie ses dégâts à l’attaquant.</t>
         </is>
       </c>
       <c r="P11" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Le voyant rouge clignote en rythme. C’est presque joli.</t>
+          <t xml:space="preserve">Tu frappes le miroir ? C’est toi que tu frappes.</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Préparation</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R11" t="inlineStr" s="1">
@@ -1113,14 +1163,19 @@
       </c>
       <c r="S11" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">005-alt.png</t>
+          <t xml:space="preserve">010.png</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/010.png</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">006</t>
+          <t xml:space="preserve">011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="1">
@@ -1145,62 +1200,62 @@
       </c>
       <c r="F12" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Commune</t>
+          <t xml:space="preserve">Peu commune</t>
         </is>
       </c>
       <c r="G12" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">●</t>
+          <t xml:space="preserve">✦</t>
         </is>
       </c>
       <c r="H12" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Bombe</t>
+          <t xml:space="preserve">Contre-attaque glaciale</t>
         </is>
       </c>
       <c r="I12" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Attaque</t>
+          <t xml:space="preserve">Contre</t>
         </is>
       </c>
       <c r="J12" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">🗡️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="K12" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#e5484d</t>
+          <t xml:space="preserve">#22b8cf</t>
         </is>
       </c>
       <c r="L12" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="M12" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Rouge</t>
+          <t xml:space="preserve">Bleu</t>
         </is>
       </c>
       <c r="N12" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#e2483d</t>
+          <t xml:space="preserve">#3fa9f5</t>
         </is>
       </c>
       <c r="O12" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Si annulée : inflige quand même 2 dégâts.</t>
+          <t xml:space="preserve">Annule une Attaque. Sinon, inflige 1 dégât.</t>
         </is>
       </c>
       <c r="P12" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Même désamorcée, elle trouve toujours un moyen de faire boum.</t>
+          <t xml:space="preserve">Le froid répond toujours. Un peu.</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Si annulée</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R12" t="inlineStr" s="1">
@@ -1210,14 +1265,19 @@
       </c>
       <c r="S12" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">006.png</t>
+          <t xml:space="preserve">011.png</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/011.png</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">006*</t>
+          <t xml:space="preserve">012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="1">
@@ -1237,67 +1297,67 @@
       </c>
       <c r="E13" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Alternative</t>
+          <t xml:space="preserve">Normale</t>
         </is>
       </c>
       <c r="F13" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Commune</t>
+          <t xml:space="preserve">Peu commune</t>
         </is>
       </c>
       <c r="G13" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">●</t>
+          <t xml:space="preserve">✦</t>
         </is>
       </c>
       <c r="H13" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Bombe</t>
+          <t xml:space="preserve">Gel</t>
         </is>
       </c>
       <c r="I13" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Attaque</t>
+          <t xml:space="preserve">Tactique</t>
         </is>
       </c>
       <c r="J13" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">🗡️</t>
+          <t xml:space="preserve">✨</t>
         </is>
       </c>
       <c r="K13" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#e5484d</t>
+          <t xml:space="preserve">#9b6dff</t>
         </is>
       </c>
       <c r="L13" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M13" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Rouge</t>
+          <t xml:space="preserve">Bleu</t>
         </is>
       </c>
       <c r="N13" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#e2483d</t>
+          <t xml:space="preserve">#3fa9f5</t>
         </is>
       </c>
       <c r="O13" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Si annulée : inflige quand même 2 dégâts.</t>
+          <t xml:space="preserve">Gel : la prochaine carte adverse est annulée.</t>
         </is>
       </c>
       <c r="P13" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Emballée dans du papier cadeau. Ne pas secouer.</t>
+          <t xml:space="preserve">Plus rien ne bouge. Même pas tes plans.</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Si annulée</t>
+          <t xml:space="preserve">Gel</t>
         </is>
       </c>
       <c r="R13" t="inlineStr" s="1">
@@ -1307,14 +1367,19 @@
       </c>
       <c r="S13" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">006-alt.png</t>
+          <t xml:space="preserve">012.png</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/012.png</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">007</t>
+          <t xml:space="preserve">013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="1">
@@ -1339,57 +1404,57 @@
       </c>
       <c r="F14" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Rare</t>
+          <t xml:space="preserve">Commune</t>
         </is>
       </c>
       <c r="G14" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">✶</t>
+          <t xml:space="preserve">●</t>
         </is>
       </c>
       <c r="H14" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Feu de barrage</t>
+          <t xml:space="preserve">Blizzard</t>
         </is>
       </c>
       <c r="I14" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Attaque</t>
+          <t xml:space="preserve">Tactique</t>
         </is>
       </c>
       <c r="J14" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">🗡️</t>
+          <t xml:space="preserve">✨</t>
         </is>
       </c>
       <c r="K14" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#e5484d</t>
+          <t xml:space="preserve">#9b6dff</t>
         </is>
       </c>
       <c r="L14" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M14" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Rouge</t>
+          <t xml:space="preserve">Bleu</t>
         </is>
       </c>
       <c r="N14" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#e2483d</t>
+          <t xml:space="preserve">#3fa9f5</t>
         </is>
       </c>
       <c r="O14" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Ne peut pas être annulée par un Contre.</t>
+          <t xml:space="preserve">Annule la carte d’en face si c’est une Attaque ou une Garde de valeur 2 ou moins.</t>
         </is>
       </c>
       <c r="P14" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Contrer ça ? Bonne chance. Il y en a partout.</t>
+          <t xml:space="preserve">Les petits coups se perdent dans la tempête.</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr" s="1">
@@ -1404,14 +1469,19 @@
       </c>
       <c r="S14" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">007.png</t>
+          <t xml:space="preserve">013.png</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/013.png</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">007*</t>
+          <t xml:space="preserve">014</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="1">
@@ -1431,62 +1501,62 @@
       </c>
       <c r="E15" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Alternative</t>
+          <t xml:space="preserve">Normale</t>
         </is>
       </c>
       <c r="F15" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Rare</t>
+          <t xml:space="preserve">Commune</t>
         </is>
       </c>
       <c r="G15" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">✶</t>
+          <t xml:space="preserve">●</t>
         </is>
       </c>
       <c r="H15" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Feu de barrage</t>
+          <t xml:space="preserve">Mur de givre</t>
         </is>
       </c>
       <c r="I15" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Attaque</t>
+          <t xml:space="preserve">Garde</t>
         </is>
       </c>
       <c r="J15" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">🗡️</t>
+          <t xml:space="preserve">🛡️</t>
         </is>
       </c>
       <c r="K15" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#e5484d</t>
+          <t xml:space="preserve">#d4a017</t>
         </is>
       </c>
       <c r="L15" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="M15" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Rouge</t>
+          <t xml:space="preserve">Bleu</t>
         </is>
       </c>
       <c r="N15" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#e2483d</t>
+          <t xml:space="preserve">#3fa9f5</t>
         </is>
       </c>
       <c r="O15" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Ne peut pas être annulée par un Contre.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="P15" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Un feu d’artifice, mais vraiment, vraiment trop près.</t>
+          <t xml:space="preserve">Construit en une nuit par des pingouins très motivés.</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr" s="1">
@@ -1501,14 +1571,19 @@
       </c>
       <c r="S15" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">007-alt.png</t>
+          <t xml:space="preserve">014.png</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/014.png</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">008</t>
+          <t xml:space="preserve">015</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="1">
@@ -1533,17 +1608,17 @@
       </c>
       <c r="F16" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Rare</t>
+          <t xml:space="preserve">Commune</t>
         </is>
       </c>
       <c r="G16" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">✶</t>
+          <t xml:space="preserve">●</t>
         </is>
       </c>
       <c r="H16" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Furie</t>
+          <t xml:space="preserve">Éclat de cristal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr" s="1">
@@ -1563,32 +1638,32 @@
       </c>
       <c r="L16" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">X</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="M16" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Rouge</t>
+          <t xml:space="preserve">Bleu</t>
         </is>
       </c>
       <c r="N16" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#e2483d</t>
+          <t xml:space="preserve">#3fa9f5</t>
         </is>
       </c>
       <c r="O16" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">X = nombre de tes Attaques déjà révélées ce tour (6 au plus).</t>
+          <t xml:space="preserve">Si la carte d’en face est une Garde : Gel (la prochaine carte adverse est annulée).</t>
         </is>
       </c>
       <c r="P16" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Plus on la provoque, plus elle cogne fort.</t>
+          <t xml:space="preserve">Brillant, tranchant, et franchement vexant.</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Gel</t>
         </is>
       </c>
       <c r="R16" t="inlineStr" s="1">
@@ -1598,14 +1673,19 @@
       </c>
       <c r="S16" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">008.png</t>
+          <t xml:space="preserve">015.png</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/015.png</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">008*</t>
+          <t xml:space="preserve">016</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="1">
@@ -1625,7 +1705,7 @@
       </c>
       <c r="E17" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Alternative</t>
+          <t xml:space="preserve">Normale</t>
         </is>
       </c>
       <c r="F17" t="inlineStr" s="1">
@@ -1640,52 +1720,52 @@
       </c>
       <c r="H17" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Furie</t>
+          <t xml:space="preserve">Prévoyance</t>
         </is>
       </c>
       <c r="I17" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Attaque</t>
+          <t xml:space="preserve">Tactique</t>
         </is>
       </c>
       <c r="J17" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">🗡️</t>
+          <t xml:space="preserve">✨</t>
         </is>
       </c>
       <c r="K17" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#e5484d</t>
+          <t xml:space="preserve">#9b6dff</t>
         </is>
       </c>
       <c r="L17" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">X</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M17" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Rouge</t>
+          <t xml:space="preserve">Bleu</t>
         </is>
       </c>
       <c r="N17" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#e2483d</t>
+          <t xml:space="preserve">#3fa9f5</t>
         </is>
       </c>
       <c r="O17" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">X = nombre de tes Attaques déjà révélées ce tour (6 au plus).</t>
+          <t xml:space="preserve">Vision 2 (regarde les prochaines cartes de la pile adverse).</t>
         </is>
       </c>
       <c r="P17" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Ne lui dis jamais « calme-toi ». Jamais.</t>
+          <t xml:space="preserve">Jimmy voit loin. Méfiez-vous de Jimmy.</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Vision</t>
         </is>
       </c>
       <c r="R17" t="inlineStr" s="1">
@@ -1695,14 +1775,19 @@
       </c>
       <c r="S17" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">008-alt.png</t>
+          <t xml:space="preserve">016.png</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/016.png</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">009</t>
+          <t xml:space="preserve">017</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="1">
@@ -1737,52 +1822,52 @@
       </c>
       <c r="H18" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Parade glacée</t>
+          <t xml:space="preserve">Spores</t>
         </is>
       </c>
       <c r="I18" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Contre</t>
+          <t xml:space="preserve">Attaque</t>
         </is>
       </c>
       <c r="J18" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🗡️</t>
         </is>
       </c>
       <c r="K18" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#22b8cf</t>
+          <t xml:space="preserve">#e5484d</t>
         </is>
       </c>
       <c r="L18" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="M18" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Bleu</t>
+          <t xml:space="preserve">Vert</t>
         </is>
       </c>
       <c r="N18" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#3fa9f5</t>
+          <t xml:space="preserve">#43c46b</t>
         </is>
       </c>
       <c r="O18" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Annule une Attaque.</t>
+          <t xml:space="preserve">Poison 2 (l’adversaire perd 1 PV à la fin de chacun des prochains duels).</t>
         </is>
       </c>
       <c r="P18" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Un pas de côté, un peu de givre, et l’attaque glisse.</t>
+          <t xml:space="preserve">Ça gratte un peu. Puis beaucoup.</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Poison</t>
         </is>
       </c>
       <c r="R18" t="inlineStr" s="1">
@@ -1792,14 +1877,19 @@
       </c>
       <c r="S18" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">009.png</t>
+          <t xml:space="preserve">017.png</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/017.png</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">009*</t>
+          <t xml:space="preserve">018</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="1">
@@ -1819,7 +1909,7 @@
       </c>
       <c r="E19" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Alternative</t>
+          <t xml:space="preserve">Normale</t>
         </is>
       </c>
       <c r="F19" t="inlineStr" s="1">
@@ -1834,22 +1924,22 @@
       </c>
       <c r="H19" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Parade glacée</t>
+          <t xml:space="preserve">Régénération</t>
         </is>
       </c>
       <c r="I19" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Contre</t>
+          <t xml:space="preserve">Tactique</t>
         </is>
       </c>
       <c r="J19" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">✨</t>
         </is>
       </c>
       <c r="K19" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#22b8cf</t>
+          <t xml:space="preserve">#9b6dff</t>
         </is>
       </c>
       <c r="L19" t="inlineStr" s="1">
@@ -1859,22 +1949,22 @@
       </c>
       <c r="M19" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Bleu</t>
+          <t xml:space="preserve">Vert</t>
         </is>
       </c>
       <c r="N19" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#3fa9f5</t>
+          <t xml:space="preserve">#43c46b</t>
         </is>
       </c>
       <c r="O19" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Annule une Attaque.</t>
+          <t xml:space="preserve">Soigne 2 PV.</t>
         </is>
       </c>
       <c r="P19" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Glisser avec élégance, c’est tout un art.</t>
+          <t xml:space="preserve">Un peu de sève, et ça repart.</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr" s="1">
@@ -1889,14 +1979,19 @@
       </c>
       <c r="S19" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">009-alt.png</t>
+          <t xml:space="preserve">018.png</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/018.png</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">010</t>
+          <t xml:space="preserve">019</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="1">
@@ -1921,64 +2016,64 @@
       </c>
       <c r="F20" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Rare</t>
+          <t xml:space="preserve">Commune</t>
         </is>
       </c>
       <c r="G20" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">✶</t>
+          <t xml:space="preserve">●</t>
         </is>
       </c>
       <c r="H20" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Miroir de glace</t>
+          <t xml:space="preserve">Carapace</t>
         </is>
       </c>
       <c r="I20" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Contre</t>
+          <t xml:space="preserve">Garde</t>
         </is>
       </c>
       <c r="J20" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🛡️</t>
         </is>
       </c>
       <c r="K20" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#22b8cf</t>
+          <t xml:space="preserve">#d4a017</t>
         </is>
       </c>
       <c r="L20" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Vert</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">#43c46b</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">+1 par Garde que tu as déjà révélée ce tour.</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Lente, têtue, et presque impossible à fendre.</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="M20" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Bleu</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#3fa9f5</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Annule une Attaque et renvoie ses dégâts à l’attaquant.</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tu frappes le miroir ? C’est toi que tu frappes.</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="R20" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Tylt</t>
@@ -1986,14 +2081,19 @@
       </c>
       <c r="S20" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">010.png</t>
+          <t xml:space="preserve">019.png</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/019.png</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">010*</t>
+          <t xml:space="preserve">020</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="1">
@@ -2013,37 +2113,37 @@
       </c>
       <c r="E21" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Alternative</t>
+          <t xml:space="preserve">Normale</t>
         </is>
       </c>
       <c r="F21" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Rare</t>
+          <t xml:space="preserve">Peu commune</t>
         </is>
       </c>
       <c r="G21" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">✶</t>
+          <t xml:space="preserve">✦</t>
         </is>
       </c>
       <c r="H21" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Miroir de glace</t>
+          <t xml:space="preserve">Lianes</t>
         </is>
       </c>
       <c r="I21" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Contre</t>
+          <t xml:space="preserve">Tactique</t>
         </is>
       </c>
       <c r="J21" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">✨</t>
         </is>
       </c>
       <c r="K21" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#22b8cf</t>
+          <t xml:space="preserve">#9b6dff</t>
         </is>
       </c>
       <c r="L21" t="inlineStr" s="1">
@@ -2053,22 +2153,22 @@
       </c>
       <c r="M21" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Bleu</t>
+          <t xml:space="preserve">Vert</t>
         </is>
       </c>
       <c r="N21" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#3fa9f5</t>
+          <t xml:space="preserve">#43c46b</t>
         </is>
       </c>
       <c r="O21" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Annule une Attaque et renvoie ses dégâts à l’attaquant.</t>
+          <t xml:space="preserve">La prochaine carte adverse a −2 de valeur.</t>
         </is>
       </c>
       <c r="P21" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Miroir, mon beau miroir… qui va encore se faire mal ?</t>
+          <t xml:space="preserve">Elles s’enroulent autour de tout ce qui bouge. Et de ce qui ne bouge pas.</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr" s="1">
@@ -2083,14 +2183,19 @@
       </c>
       <c r="S21" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">010-alt.png</t>
+          <t xml:space="preserve">020.png</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/020.png</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">011</t>
+          <t xml:space="preserve">021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="1">
@@ -2115,62 +2220,62 @@
       </c>
       <c r="F22" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Peu commune</t>
+          <t xml:space="preserve">Commune</t>
         </is>
       </c>
       <c r="G22" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">✦</t>
+          <t xml:space="preserve">●</t>
         </is>
       </c>
       <c r="H22" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Contre-attaque glaciale</t>
+          <t xml:space="preserve">Morsure de la Nuée</t>
         </is>
       </c>
       <c r="I22" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Contre</t>
+          <t xml:space="preserve">Attaque</t>
         </is>
       </c>
       <c r="J22" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🗡️</t>
         </is>
       </c>
       <c r="K22" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#22b8cf</t>
+          <t xml:space="preserve">#e5484d</t>
         </is>
       </c>
       <c r="L22" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="M22" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Bleu</t>
+          <t xml:space="preserve">Vert</t>
         </is>
       </c>
       <c r="N22" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#3fa9f5</t>
+          <t xml:space="preserve">#43c46b</t>
         </is>
       </c>
       <c r="O22" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Annule une Attaque. Sinon, inflige 1 dégât.</t>
+          <t xml:space="preserve">Vol de vie (tu regagnes les PV infligés).</t>
         </is>
       </c>
       <c r="P22" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Le froid répond toujours. Un peu.</t>
+          <t xml:space="preserve">La Nuée a toujours faim. Toujours.</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Vol de vie</t>
         </is>
       </c>
       <c r="R22" t="inlineStr" s="1">
@@ -2180,14 +2285,19 @@
       </c>
       <c r="S22" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">011.png</t>
+          <t xml:space="preserve">021.png</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/021.png</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">011*</t>
+          <t xml:space="preserve">022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="1">
@@ -2207,7 +2317,7 @@
       </c>
       <c r="E23" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Alternative</t>
+          <t xml:space="preserve">Normale</t>
         </is>
       </c>
       <c r="F23" t="inlineStr" s="1">
@@ -2222,7 +2332,7 @@
       </c>
       <c r="H23" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Contre-attaque glaciale</t>
+          <t xml:space="preserve">Pollen</t>
         </is>
       </c>
       <c r="I23" t="inlineStr" s="1">
@@ -2242,27 +2352,27 @@
       </c>
       <c r="L23" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M23" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Bleu</t>
+          <t xml:space="preserve">Vert</t>
         </is>
       </c>
       <c r="N23" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#3fa9f5</t>
+          <t xml:space="preserve">#43c46b</t>
         </is>
       </c>
       <c r="O23" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Annule une Attaque. Sinon, inflige 1 dégât.</t>
+          <t xml:space="preserve">Annule une Attaque ; si c’est le cas, soigne 1 PV.</t>
         </is>
       </c>
       <c r="P23" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Un coup de froid, avec un petit supplément.</t>
+          <t xml:space="preserve">Atchoum ! L’attaque est partie… ailleurs.</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr" s="1">
@@ -2277,14 +2387,19 @@
       </c>
       <c r="S23" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">011-alt.png</t>
+          <t xml:space="preserve">022.png</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/022.png</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">012</t>
+          <t xml:space="preserve">023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="1">
@@ -2309,62 +2424,62 @@
       </c>
       <c r="F24" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Peu commune</t>
+          <t xml:space="preserve">Rare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">✦</t>
+          <t xml:space="preserve">✶</t>
         </is>
       </c>
       <c r="H24" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Gel</t>
+          <t xml:space="preserve">Essaim</t>
         </is>
       </c>
       <c r="I24" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Tactique</t>
+          <t xml:space="preserve">Attaque</t>
         </is>
       </c>
       <c r="J24" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">✨</t>
+          <t xml:space="preserve">🗡️</t>
         </is>
       </c>
       <c r="K24" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#9b6dff</t>
+          <t xml:space="preserve">#e5484d</t>
         </is>
       </c>
       <c r="L24" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="M24" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Bleu</t>
+          <t xml:space="preserve">Vert</t>
         </is>
       </c>
       <c r="N24" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#3fa9f5</t>
+          <t xml:space="preserve">#43c46b</t>
         </is>
       </c>
       <c r="O24" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Gel : la prochaine carte adverse est annulée.</t>
+          <t xml:space="preserve">Si annulée : Poison 2 (l’adversaire perd 1 PV à la fin de chacun des prochains duels).</t>
         </is>
       </c>
       <c r="P24" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Plus rien ne bouge. Même pas tes plans.</t>
+          <t xml:space="preserve">On en écrase un, il en arrive dix.</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Gel</t>
+          <t xml:space="preserve">Si annulée, Poison</t>
         </is>
       </c>
       <c r="R24" t="inlineStr" s="1">
@@ -2374,14 +2489,19 @@
       </c>
       <c r="S24" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">012.png</t>
+          <t xml:space="preserve">023.png</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/023.png</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">012*</t>
+          <t xml:space="preserve">024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="1">
@@ -2401,22 +2521,22 @@
       </c>
       <c r="E25" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Alternative</t>
+          <t xml:space="preserve">Normale</t>
         </is>
       </c>
       <c r="F25" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Peu commune</t>
+          <t xml:space="preserve">Rare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">✦</t>
+          <t xml:space="preserve">✶</t>
         </is>
       </c>
       <c r="H25" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Gel</t>
+          <t xml:space="preserve">Floraison</t>
         </is>
       </c>
       <c r="I25" t="inlineStr" s="1">
@@ -2441,27 +2561,27 @@
       </c>
       <c r="M25" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Bleu</t>
+          <t xml:space="preserve">Vert</t>
         </is>
       </c>
       <c r="N25" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#3fa9f5</t>
+          <t xml:space="preserve">#43c46b</t>
         </is>
       </c>
       <c r="O25" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Gel : la prochaine carte adverse est annulée.</t>
+          <t xml:space="preserve">Soigne 1 PV par carte Verte que tu as déjà révélée ce tour.</t>
         </is>
       </c>
       <c r="P25" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Même les étoiles s’arrêtent pour regarder.</t>
+          <t xml:space="preserve">Au printemps de Spore, tout repousse. Même les blessures.</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Gel</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R25" t="inlineStr" s="1">
@@ -2471,14 +2591,19 @@
       </c>
       <c r="S25" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">012-alt.png</t>
+          <t xml:space="preserve">024.png</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/024.png</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">013</t>
+          <t xml:space="preserve">025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="1">
@@ -2513,47 +2638,47 @@
       </c>
       <c r="H26" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Blizzard</t>
+          <t xml:space="preserve">Bouclier solaire</t>
         </is>
       </c>
       <c r="I26" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Tactique</t>
+          <t xml:space="preserve">Garde</t>
         </is>
       </c>
       <c r="J26" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">✨</t>
+          <t xml:space="preserve">🛡️</t>
         </is>
       </c>
       <c r="K26" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#9b6dff</t>
+          <t xml:space="preserve">#d4a017</t>
         </is>
       </c>
       <c r="L26" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Jaune</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">#f5c02e</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="M26" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Bleu</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#3fa9f5</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Annule la carte d’en face si c’est une Attaque ou une Garde de valeur 2 ou moins.</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Les petits coups se perdent dans la tempête.</t>
+          <t xml:space="preserve">Le soleil protège ceux qui savent l’attendre.</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr" s="1">
@@ -2568,14 +2693,19 @@
       </c>
       <c r="S26" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">013.png</t>
+          <t xml:space="preserve">025.png</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/025.png</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">013*</t>
+          <t xml:space="preserve">026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="1">
@@ -2595,69 +2725,69 @@
       </c>
       <c r="E27" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Alternative</t>
+          <t xml:space="preserve">Normale</t>
         </is>
       </c>
       <c r="F27" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Commune</t>
+          <t xml:space="preserve">Peu commune</t>
         </is>
       </c>
       <c r="G27" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">●</t>
+          <t xml:space="preserve">✦</t>
         </is>
       </c>
       <c r="H27" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Blizzard</t>
+          <t xml:space="preserve">Rempart</t>
         </is>
       </c>
       <c r="I27" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Tactique</t>
+          <t xml:space="preserve">Garde</t>
         </is>
       </c>
       <c r="J27" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">✨</t>
+          <t xml:space="preserve">🛡️</t>
         </is>
       </c>
       <c r="K27" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#9b6dff</t>
+          <t xml:space="preserve">#d4a017</t>
         </is>
       </c>
       <c r="L27" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Jaune</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">#f5c02e</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Le bouclier n’arrive qu’après les dégâts de ce duel.</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Lent à monter. Impossible à faire tomber.</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="M27" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Bleu</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#3fa9f5</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Annule la carte d’en face si c’est une Attaque ou une Garde de valeur 2 ou moins.</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Dehors, il fait −200°. Dedans aussi.</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="R27" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Tylt</t>
@@ -2665,14 +2795,19 @@
       </c>
       <c r="S27" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">013-alt.png</t>
+          <t xml:space="preserve">026.png</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/026.png</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">014</t>
+          <t xml:space="preserve">027</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="1">
@@ -2707,7 +2842,7 @@
       </c>
       <c r="H28" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Mur de givre</t>
+          <t xml:space="preserve">Épines dorées</t>
         </is>
       </c>
       <c r="I28" t="inlineStr" s="1">
@@ -2727,32 +2862,32 @@
       </c>
       <c r="L28" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="M28" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Bleu</t>
+          <t xml:space="preserve">Jaune</t>
         </is>
       </c>
       <c r="N28" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#3fa9f5</t>
+          <t xml:space="preserve">#f5c02e</t>
         </is>
       </c>
       <c r="O28" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Épines 2 : si une Attaque adverse te touche pendant ce duel, son attaquant subit 2 dégâts.</t>
         </is>
       </c>
       <c r="P28" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Construit en une nuit par des pingouins très motivés.</t>
+          <t xml:space="preserve">Touche-moi si tu l’oses. Vraiment, ose.</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Épines</t>
         </is>
       </c>
       <c r="R28" t="inlineStr" s="1">
@@ -2762,14 +2897,19 @@
       </c>
       <c r="S28" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">014.png</t>
+          <t xml:space="preserve">027.png</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/027.png</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">014*</t>
+          <t xml:space="preserve">028</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="1">
@@ -2789,22 +2929,22 @@
       </c>
       <c r="E29" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Alternative</t>
+          <t xml:space="preserve">Normale</t>
         </is>
       </c>
       <c r="F29" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Commune</t>
+          <t xml:space="preserve">Rare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">●</t>
+          <t xml:space="preserve">✶</t>
         </is>
       </c>
       <c r="H29" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Mur de givre</t>
+          <t xml:space="preserve">Bouclier galactique</t>
         </is>
       </c>
       <c r="I29" t="inlineStr" s="1">
@@ -2824,34 +2964,34 @@
       </c>
       <c r="L29" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="M29" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Bleu</t>
+          <t xml:space="preserve">Jaune</t>
         </is>
       </c>
       <c r="N29" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#3fa9f5</t>
+          <t xml:space="preserve">#f5c02e</t>
         </is>
       </c>
       <c r="O29" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">Ton bouclier ne disparaît pas à la fin du tour.</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Le Bouclier tient depuis mille ans. Il tiendra bien un tour de plus.</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="P29" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Les pingouins l’ont décoré. Ils en sont très fiers.</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="R29" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Tylt</t>
@@ -2859,14 +2999,19 @@
       </c>
       <c r="S29" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">014-alt.png</t>
+          <t xml:space="preserve">028.png</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/028.png</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">015</t>
+          <t xml:space="preserve">029</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="1">
@@ -2901,7 +3046,7 @@
       </c>
       <c r="H30" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Éclat de cristal</t>
+          <t xml:space="preserve">Éclat solaire</t>
         </is>
       </c>
       <c r="I30" t="inlineStr" s="1">
@@ -2921,32 +3066,32 @@
       </c>
       <c r="L30" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">X</t>
         </is>
       </c>
       <c r="M30" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Bleu</t>
+          <t xml:space="preserve">Jaune</t>
         </is>
       </c>
       <c r="N30" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#3fa9f5</t>
+          <t xml:space="preserve">#f5c02e</t>
         </is>
       </c>
       <c r="O30" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Si la carte d’en face est une Garde : Gel (la prochaine carte adverse est annulée).</t>
+          <t xml:space="preserve">X = ton bouclier actuel (6 au plus). Le bouclier n’est pas dépensé.</t>
         </is>
       </c>
       <c r="P30" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Brillant, tranchant, et franchement vexant.</t>
+          <t xml:space="preserve">Toute la lumière qu’il a gardée, il te la renvoie d’un coup.</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Gel</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R30" t="inlineStr" s="1">
@@ -2956,14 +3101,19 @@
       </c>
       <c r="S30" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">015.png</t>
+          <t xml:space="preserve">029.png</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/029.png</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">015*</t>
+          <t xml:space="preserve">030</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="1">
@@ -2983,67 +3133,67 @@
       </c>
       <c r="E31" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Alternative</t>
+          <t xml:space="preserve">Normale</t>
         </is>
       </c>
       <c r="F31" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Commune</t>
+          <t xml:space="preserve">Rare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">●</t>
+          <t xml:space="preserve">✶</t>
         </is>
       </c>
       <c r="H31" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Éclat de cristal</t>
+          <t xml:space="preserve">Bénédiction</t>
         </is>
       </c>
       <c r="I31" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Attaque</t>
+          <t xml:space="preserve">Tactique</t>
         </is>
       </c>
       <c r="J31" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">🗡️</t>
+          <t xml:space="preserve">✨</t>
         </is>
       </c>
       <c r="K31" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#e5484d</t>
+          <t xml:space="preserve">#9b6dff</t>
         </is>
       </c>
       <c r="L31" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M31" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Bleu</t>
+          <t xml:space="preserve">Jaune</t>
         </is>
       </c>
       <c r="N31" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#3fa9f5</t>
+          <t xml:space="preserve">#f5c02e</t>
         </is>
       </c>
       <c r="O31" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Si la carte d’en face est une Garde : Gel (la prochaine carte adverse est annulée).</t>
+          <t xml:space="preserve">Double ton bouclier (10 au plus).</t>
         </is>
       </c>
       <c r="P31" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Taillé à la main par un artisan des glaces. Très, très pointu.</t>
+          <t xml:space="preserve">Deux fois plus de lumière, deux fois plus de soucis pour toi.</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Gel</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R31" t="inlineStr" s="1">
@@ -3053,14 +3203,19 @@
       </c>
       <c r="S31" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">015-alt.png</t>
+          <t xml:space="preserve">030.png</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/030.png</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">016</t>
+          <t xml:space="preserve">031</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="1">
@@ -3085,32 +3240,32 @@
       </c>
       <c r="F32" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Rare</t>
+          <t xml:space="preserve">Commune</t>
         </is>
       </c>
       <c r="G32" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">✶</t>
+          <t xml:space="preserve">●</t>
         </is>
       </c>
       <c r="H32" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Prévoyance</t>
+          <t xml:space="preserve">Garde galactique</t>
         </is>
       </c>
       <c r="I32" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Tactique</t>
+          <t xml:space="preserve">Contre</t>
         </is>
       </c>
       <c r="J32" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">✨</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="K32" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#9b6dff</t>
+          <t xml:space="preserve">#22b8cf</t>
         </is>
       </c>
       <c r="L32" t="inlineStr" s="1">
@@ -3120,27 +3275,27 @@
       </c>
       <c r="M32" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Bleu</t>
+          <t xml:space="preserve">Jaune</t>
         </is>
       </c>
       <c r="N32" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#3fa9f5</t>
+          <t xml:space="preserve">#f5c02e</t>
         </is>
       </c>
       <c r="O32" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Vision 2 (regarde les prochaines cartes de la pile adverse).</t>
+          <t xml:space="preserve">Annule une Attaque ; si c’est le cas, gagne 2 de bouclier.</t>
         </is>
       </c>
       <c r="P32" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Jimmy voit loin. Méfiez-vous de Jimmy.</t>
+          <t xml:space="preserve">Halte ! Plus personne ne passe.</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Vision</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R32" t="inlineStr" s="1">
@@ -3150,14 +3305,19 @@
       </c>
       <c r="S32" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">016.png</t>
+          <t xml:space="preserve">031.png</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/031.png</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">016*</t>
+          <t xml:space="preserve">032</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="1">
@@ -3177,22 +3337,22 @@
       </c>
       <c r="E33" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Alternative</t>
+          <t xml:space="preserve">Normale</t>
         </is>
       </c>
       <c r="F33" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Rare</t>
+          <t xml:space="preserve">Peu commune</t>
         </is>
       </c>
       <c r="G33" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">✶</t>
+          <t xml:space="preserve">✦</t>
         </is>
       </c>
       <c r="H33" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Prévoyance</t>
+          <t xml:space="preserve">Aveuglement</t>
         </is>
       </c>
       <c r="I33" t="inlineStr" s="1">
@@ -3217,27 +3377,27 @@
       </c>
       <c r="M33" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Bleu</t>
+          <t xml:space="preserve">Jaune</t>
         </is>
       </c>
       <c r="N33" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#3fa9f5</t>
+          <t xml:space="preserve">#f5c02e</t>
         </is>
       </c>
       <c r="O33" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Vision 2 (regarde les prochaines cartes de la pile adverse).</t>
+          <t xml:space="preserve">La prochaine Attaque adverse fait −3.</t>
         </is>
       </c>
       <c r="P33" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Jimmy a vu ta carte avant toi. Et il sourit.</t>
+          <t xml:space="preserve">Attention à la tête… et surtout aux yeux.</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Vision</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R33" t="inlineStr" s="1">
@@ -3247,14 +3407,19 @@
       </c>
       <c r="S33" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">016-alt.png</t>
+          <t xml:space="preserve">032.png</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/032.png</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">017</t>
+          <t xml:space="preserve">033</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="1">
@@ -3279,62 +3444,62 @@
       </c>
       <c r="F34" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Commune</t>
+          <t xml:space="preserve">Rare</t>
         </is>
       </c>
       <c r="G34" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">●</t>
+          <t xml:space="preserve">✶</t>
         </is>
       </c>
       <c r="H34" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Spores</t>
+          <t xml:space="preserve">Télépathie</t>
         </is>
       </c>
       <c r="I34" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Attaque</t>
+          <t xml:space="preserve">Tactique</t>
         </is>
       </c>
       <c r="J34" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">🗡️</t>
+          <t xml:space="preserve">✨</t>
         </is>
       </c>
       <c r="K34" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#e5484d</t>
+          <t xml:space="preserve">#9b6dff</t>
         </is>
       </c>
       <c r="L34" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M34" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Vert</t>
+          <t xml:space="preserve">Violet</t>
         </is>
       </c>
       <c r="N34" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#43c46b</t>
+          <t xml:space="preserve">#a35cff</t>
         </is>
       </c>
       <c r="O34" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Poison 2 (l’adversaire perd 1 PV à la fin de chacun des prochains duels).</t>
+          <t xml:space="preserve">Vision 2 (regarde les prochaines cartes de la pile adverse), puis tu peux échanger tes 2 prochaines cartes.</t>
         </is>
       </c>
       <c r="P34" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Ça gratte un peu. Puis beaucoup.</t>
+          <t xml:space="preserve">Jimmy sait ce que tu vas jouer. Jimmy sait tout.</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Poison</t>
+          <t xml:space="preserve">Vision, Échange</t>
         </is>
       </c>
       <c r="R34" t="inlineStr" s="1">
@@ -3344,14 +3509,19 @@
       </c>
       <c r="S34" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">017.png</t>
+          <t xml:space="preserve">033.png</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/033.png</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">017*</t>
+          <t xml:space="preserve">034</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="1">
@@ -3371,67 +3541,67 @@
       </c>
       <c r="E35" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Alternative</t>
+          <t xml:space="preserve">Normale</t>
         </is>
       </c>
       <c r="F35" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Commune</t>
+          <t xml:space="preserve">Peu commune</t>
         </is>
       </c>
       <c r="G35" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">●</t>
+          <t xml:space="preserve">✦</t>
         </is>
       </c>
       <c r="H35" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Spores</t>
+          <t xml:space="preserve">Tour de passe-passe</t>
         </is>
       </c>
       <c r="I35" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Attaque</t>
+          <t xml:space="preserve">Tactique</t>
         </is>
       </c>
       <c r="J35" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">🗡️</t>
+          <t xml:space="preserve">✨</t>
         </is>
       </c>
       <c r="K35" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#e5484d</t>
+          <t xml:space="preserve">#9b6dff</t>
         </is>
       </c>
       <c r="L35" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M35" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Vert</t>
+          <t xml:space="preserve">Violet</t>
         </is>
       </c>
       <c r="N35" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#43c46b</t>
+          <t xml:space="preserve">#a35cff</t>
         </is>
       </c>
       <c r="O35" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Poison 2 (l’adversaire perd 1 PV à la fin de chacun des prochains duels).</t>
+          <t xml:space="preserve">Échange les 2 prochaines cartes de l’adversaire, puis Vision 2 (regarde les prochaines cartes de la pile adverse).</t>
         </is>
       </c>
       <c r="P35" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Ne pas respirer. Surtout ne pas respirer.</t>
+          <t xml:space="preserve">Tu étais sûr de l’ordre de tes cartes ? Tu l’étais.</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Poison</t>
+          <t xml:space="preserve">Échange, Vision</t>
         </is>
       </c>
       <c r="R35" t="inlineStr" s="1">
@@ -3441,14 +3611,19 @@
       </c>
       <c r="S35" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">017-alt.png</t>
+          <t xml:space="preserve">034.png</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/034.png</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">018</t>
+          <t xml:space="preserve">035</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="1">
@@ -3483,54 +3658,54 @@
       </c>
       <c r="H36" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Régénération</t>
+          <t xml:space="preserve">Rayon néon</t>
         </is>
       </c>
       <c r="I36" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Tactique</t>
+          <t xml:space="preserve">Attaque</t>
         </is>
       </c>
       <c r="J36" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">✨</t>
+          <t xml:space="preserve">🗡️</t>
         </is>
       </c>
       <c r="K36" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#9b6dff</t>
+          <t xml:space="preserve">#e5484d</t>
         </is>
       </c>
       <c r="L36" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Violet</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">#a35cff</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">+2 si tu avais vu cette carte adverse grâce à une Vision (regarde les prochaines cartes de la pile adverse).</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Il t’a vu venir. De très loin.</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="M36" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Vert</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#43c46b</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Soigne 2 PV.</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Un peu de sève, et ça repart.</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="R36" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Tylt</t>
@@ -3538,14 +3713,19 @@
       </c>
       <c r="S36" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">018.png</t>
+          <t xml:space="preserve">035.png</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/035.png</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">018*</t>
+          <t xml:space="preserve">036</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="1">
@@ -3565,37 +3745,37 @@
       </c>
       <c r="E37" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Alternative</t>
+          <t xml:space="preserve">Normale</t>
         </is>
       </c>
       <c r="F37" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Commune</t>
+          <t xml:space="preserve">Peu commune</t>
         </is>
       </c>
       <c r="G37" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">●</t>
+          <t xml:space="preserve">✦</t>
         </is>
       </c>
       <c r="H37" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Régénération</t>
+          <t xml:space="preserve">Mirage</t>
         </is>
       </c>
       <c r="I37" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Tactique</t>
+          <t xml:space="preserve">Contre</t>
         </is>
       </c>
       <c r="J37" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">✨</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="K37" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#9b6dff</t>
+          <t xml:space="preserve">#22b8cf</t>
         </is>
       </c>
       <c r="L37" t="inlineStr" s="1">
@@ -3605,22 +3785,22 @@
       </c>
       <c r="M37" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Vert</t>
+          <t xml:space="preserve">Violet</t>
         </is>
       </c>
       <c r="N37" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#43c46b</t>
+          <t xml:space="preserve">#a35cff</t>
         </is>
       </c>
       <c r="O37" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Soigne 2 PV.</t>
+          <t xml:space="preserve">Annule une Attaque ou une Tactique.</t>
         </is>
       </c>
       <c r="P37" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Une tisane de spores, et tout va mieux.</t>
+          <t xml:space="preserve">Tu frappes… du vide.</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr" s="1">
@@ -3635,14 +3815,19 @@
       </c>
       <c r="S37" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">018-alt.png</t>
+          <t xml:space="preserve">036.png</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/036.png</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">019</t>
+          <t xml:space="preserve">037</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="1">
@@ -3667,57 +3852,57 @@
       </c>
       <c r="F38" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Commune</t>
+          <t xml:space="preserve">Rare</t>
         </is>
       </c>
       <c r="G38" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">●</t>
+          <t xml:space="preserve">✶</t>
         </is>
       </c>
       <c r="H38" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Carapace</t>
+          <t xml:space="preserve">Copie</t>
         </is>
       </c>
       <c r="I38" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Garde</t>
+          <t xml:space="preserve">Tactique</t>
         </is>
       </c>
       <c r="J38" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">🛡️</t>
+          <t xml:space="preserve">✨</t>
         </is>
       </c>
       <c r="K38" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#d4a017</t>
+          <t xml:space="preserve">#9b6dff</t>
         </is>
       </c>
       <c r="L38" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M38" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Vert</t>
+          <t xml:space="preserve">Violet</t>
         </is>
       </c>
       <c r="N38" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#43c46b</t>
+          <t xml:space="preserve">#a35cff</t>
         </is>
       </c>
       <c r="O38" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">+1 par Garde que tu as déjà révélée ce tour.</t>
+          <t xml:space="preserve">Devient une copie de la carte d’en face.</t>
         </is>
       </c>
       <c r="P38" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Lente, têtue, et presque impossible à fendre.</t>
+          <t xml:space="preserve">Ce que tu fais, je le fais. En mieux.</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr" s="1">
@@ -3732,14 +3917,19 @@
       </c>
       <c r="S38" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">019.png</t>
+          <t xml:space="preserve">037.png</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/037.png</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">019*</t>
+          <t xml:space="preserve">038</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="1">
@@ -3759,7 +3949,7 @@
       </c>
       <c r="E39" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Alternative</t>
+          <t xml:space="preserve">Normale</t>
         </is>
       </c>
       <c r="F39" t="inlineStr" s="1">
@@ -3774,22 +3964,22 @@
       </c>
       <c r="H39" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Carapace</t>
+          <t xml:space="preserve">Chaos</t>
         </is>
       </c>
       <c r="I39" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Garde</t>
+          <t xml:space="preserve">Attaque</t>
         </is>
       </c>
       <c r="J39" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">🛡️</t>
+          <t xml:space="preserve">🗡️</t>
         </is>
       </c>
       <c r="K39" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#d4a017</t>
+          <t xml:space="preserve">#e5484d</t>
         </is>
       </c>
       <c r="L39" t="inlineStr" s="1">
@@ -3799,22 +3989,22 @@
       </c>
       <c r="M39" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Vert</t>
+          <t xml:space="preserve">Violet</t>
         </is>
       </c>
       <c r="N39" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#43c46b</t>
+          <t xml:space="preserve">#a35cff</t>
         </is>
       </c>
       <c r="O39" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">+1 par Garde que tu as déjà révélée ce tour.</t>
+          <t xml:space="preserve">Inverse l’ordre des 3 prochaines cartes de l’adversaire.</t>
         </is>
       </c>
       <c r="P39" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Elle a vu passer trois empires. Elle les a tous enterrés.</t>
+          <t xml:space="preserve">Tout ce que tu avais prévu ? À l’envers.</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr" s="1">
@@ -3829,14 +4019,19 @@
       </c>
       <c r="S39" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">019-alt.png</t>
+          <t xml:space="preserve">038.png</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/038.png</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">020</t>
+          <t xml:space="preserve">039</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="1">
@@ -3861,64 +4056,64 @@
       </c>
       <c r="F40" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Peu commune</t>
+          <t xml:space="preserve">Commune</t>
         </is>
       </c>
       <c r="G40" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">✦</t>
+          <t xml:space="preserve">●</t>
         </is>
       </c>
       <c r="H40" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Lianes</t>
+          <t xml:space="preserve">Rayon miroir</t>
         </is>
       </c>
       <c r="I40" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Tactique</t>
+          <t xml:space="preserve">Attaque</t>
         </is>
       </c>
       <c r="J40" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">✨</t>
+          <t xml:space="preserve">🗡️</t>
         </is>
       </c>
       <c r="K40" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#9b6dff</t>
+          <t xml:space="preserve">#e5484d</t>
         </is>
       </c>
       <c r="L40" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Violet</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">#a35cff</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">+2 si la carte d’en face est une Tactique.</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Les ruses se retournent toujours contre leur auteur.</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="M40" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Vert</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#43c46b</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">La prochaine carte adverse a −2 de valeur.</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Elles s’enroulent autour de tout ce qui bouge. Et de ce qui ne bouge pas.</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="R40" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Tylt</t>
@@ -3926,14 +4121,19 @@
       </c>
       <c r="S40" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">020.png</t>
+          <t xml:space="preserve">039.png</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/039.png</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">020*</t>
+          <t xml:space="preserve">040</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="1">
@@ -3953,22 +4153,22 @@
       </c>
       <c r="E41" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Alternative</t>
+          <t xml:space="preserve">Normale</t>
         </is>
       </c>
       <c r="F41" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Peu commune</t>
+          <t xml:space="preserve">Commune</t>
         </is>
       </c>
       <c r="G41" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">✦</t>
+          <t xml:space="preserve">●</t>
         </is>
       </c>
       <c r="H41" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Lianes</t>
+          <t xml:space="preserve">Déjà-vu</t>
         </is>
       </c>
       <c r="I41" t="inlineStr" s="1">
@@ -3993,22 +4193,22 @@
       </c>
       <c r="M41" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Vert</t>
+          <t xml:space="preserve">Violet</t>
         </is>
       </c>
       <c r="N41" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#43c46b</t>
+          <t xml:space="preserve">#a35cff</t>
         </is>
       </c>
       <c r="O41" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">La prochaine carte adverse a −2 de valeur.</t>
+          <t xml:space="preserve">Devient une copie de ta carte précédente.</t>
         </is>
       </c>
       <c r="P41" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Elles ont poussé pendant que tu réfléchissais.</t>
+          <t xml:space="preserve">Tu as l’impression d’avoir déjà vu cette carte ? Normal.</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr" s="1">
@@ -4023,14 +4223,19 @@
       </c>
       <c r="S41" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">020-alt.png</t>
+          <t xml:space="preserve">040.png</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/040.png</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">021</t>
+          <t xml:space="preserve">041</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="1">
@@ -4065,7 +4270,7 @@
       </c>
       <c r="H42" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Morsure de la Nuée</t>
+          <t xml:space="preserve">Lame des abysses</t>
         </is>
       </c>
       <c r="I42" t="inlineStr" s="1">
@@ -4085,32 +4290,32 @@
       </c>
       <c r="L42" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="M42" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Vert</t>
+          <t xml:space="preserve">Noir</t>
         </is>
       </c>
       <c r="N42" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#43c46b</t>
+          <t xml:space="preserve">#6b6f80</t>
         </is>
       </c>
       <c r="O42" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Vol de vie (tu regagnes les PV infligés).</t>
+          <t xml:space="preserve">Perforant (ignore le bouclier). Sacrifice 1 (tu perds ces PV, le bouclier ne les absorbe pas).</t>
         </is>
       </c>
       <c r="P42" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">La Nuée a toujours faim. Toujours.</t>
+          <t xml:space="preserve">Chaque coup se paie. Celui-là en vaut la peine.</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Vol de vie</t>
+          <t xml:space="preserve">Perforant, Sacrifice</t>
         </is>
       </c>
       <c r="R42" t="inlineStr" s="1">
@@ -4120,14 +4325,19 @@
       </c>
       <c r="S42" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">021.png</t>
+          <t xml:space="preserve">041.png</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/041.png</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">021*</t>
+          <t xml:space="preserve">042</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="1">
@@ -4147,7 +4357,7 @@
       </c>
       <c r="E43" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Alternative</t>
+          <t xml:space="preserve">Normale</t>
         </is>
       </c>
       <c r="F43" t="inlineStr" s="1">
@@ -4162,52 +4372,52 @@
       </c>
       <c r="H43" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Morsure de la Nuée</t>
+          <t xml:space="preserve">Brise-bouclier</t>
         </is>
       </c>
       <c r="I43" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Attaque</t>
+          <t xml:space="preserve">Tactique</t>
         </is>
       </c>
       <c r="J43" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">🗡️</t>
+          <t xml:space="preserve">✨</t>
         </is>
       </c>
       <c r="K43" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#e5484d</t>
+          <t xml:space="preserve">#9b6dff</t>
         </is>
       </c>
       <c r="L43" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M43" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Vert</t>
+          <t xml:space="preserve">Noir</t>
         </is>
       </c>
       <c r="N43" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#43c46b</t>
+          <t xml:space="preserve">#6b6f80</t>
         </is>
       </c>
       <c r="O43" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Vol de vie (tu regagnes les PV infligés).</t>
+          <t xml:space="preserve">Détruit tout le bouclier adverse.</t>
         </is>
       </c>
       <c r="P43" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Une bouchée, juste une petite bouchée.</t>
+          <t xml:space="preserve">Plus de bouclier. Plus d’excuses.</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Vol de vie</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R43" t="inlineStr" s="1">
@@ -4217,14 +4427,19 @@
       </c>
       <c r="S43" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">021-alt.png</t>
+          <t xml:space="preserve">042.png</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/042.png</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">022</t>
+          <t xml:space="preserve">043</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="1">
@@ -4259,22 +4474,22 @@
       </c>
       <c r="H44" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Pollen</t>
+          <t xml:space="preserve">Malédiction</t>
         </is>
       </c>
       <c r="I44" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Contre</t>
+          <t xml:space="preserve">Tactique</t>
         </is>
       </c>
       <c r="J44" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">✨</t>
         </is>
       </c>
       <c r="K44" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#22b8cf</t>
+          <t xml:space="preserve">#9b6dff</t>
         </is>
       </c>
       <c r="L44" t="inlineStr" s="1">
@@ -4284,22 +4499,22 @@
       </c>
       <c r="M44" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Vert</t>
+          <t xml:space="preserve">Noir</t>
         </is>
       </c>
       <c r="N44" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#43c46b</t>
+          <t xml:space="preserve">#6b6f80</t>
         </is>
       </c>
       <c r="O44" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Annule une Attaque ; si c’est le cas, soigne 1 PV.</t>
+          <t xml:space="preserve">L’adversaire ne gagne ni bouclier ni PV pendant les 3 duels suivants.</t>
         </is>
       </c>
       <c r="P44" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Atchoum ! L’attaque est partie… ailleurs.</t>
+          <t xml:space="preserve">Les abysses n’oublient jamais un affront.</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr" s="1">
@@ -4314,14 +4529,19 @@
       </c>
       <c r="S44" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">022.png</t>
+          <t xml:space="preserve">043.png</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/043.png</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">022*</t>
+          <t xml:space="preserve">044</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="1">
@@ -4341,7 +4561,7 @@
       </c>
       <c r="E45" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Alternative</t>
+          <t xml:space="preserve">Normale</t>
         </is>
       </c>
       <c r="F45" t="inlineStr" s="1">
@@ -4356,22 +4576,22 @@
       </c>
       <c r="H45" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Pollen</t>
+          <t xml:space="preserve">Pacte</t>
         </is>
       </c>
       <c r="I45" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Contre</t>
+          <t xml:space="preserve">Tactique</t>
         </is>
       </c>
       <c r="J45" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">✨</t>
         </is>
       </c>
       <c r="K45" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#22b8cf</t>
+          <t xml:space="preserve">#9b6dff</t>
         </is>
       </c>
       <c r="L45" t="inlineStr" s="1">
@@ -4381,27 +4601,27 @@
       </c>
       <c r="M45" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Vert</t>
+          <t xml:space="preserve">Noir</t>
         </is>
       </c>
       <c r="N45" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#43c46b</t>
+          <t xml:space="preserve">#6b6f80</t>
         </is>
       </c>
       <c r="O45" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Annule une Attaque ; si c’est le cas, soigne 1 PV.</t>
+          <t xml:space="preserve">Sacrifice 2 (tu perds ces PV, le bouclier ne les absorbe pas). Préparation : ta prochaine Attaque fait le double.</t>
         </is>
       </c>
       <c r="P45" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Rhume des foins galactique : ne pas approcher.</t>
+          <t xml:space="preserve">Un peu de toi pour beaucoup de moi.</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Sacrifice, Préparation</t>
         </is>
       </c>
       <c r="R45" t="inlineStr" s="1">
@@ -4411,14 +4631,19 @@
       </c>
       <c r="S45" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">022-alt.png</t>
+          <t xml:space="preserve">044.png</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/044.png</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">023</t>
+          <t xml:space="preserve">045</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="1">
@@ -4453,7 +4678,7 @@
       </c>
       <c r="H46" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Essaim</t>
+          <t xml:space="preserve">Exécution</t>
         </is>
       </c>
       <c r="I46" t="inlineStr" s="1">
@@ -4478,27 +4703,27 @@
       </c>
       <c r="M46" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Vert</t>
+          <t xml:space="preserve">Noir</t>
         </is>
       </c>
       <c r="N46" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#43c46b</t>
+          <t xml:space="preserve">#6b6f80</t>
         </is>
       </c>
       <c r="O46" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Si annulée : Poison 2 (l’adversaire perd 1 PV à la fin de chacun des prochains duels).</t>
+          <t xml:space="preserve">Fait 8 si l’adversaire a 8 PV ou moins.</t>
         </is>
       </c>
       <c r="P46" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">On en écrase un, il en arrive dix.</t>
+          <t xml:space="preserve">Quand la fin approche, elle frappe plus fort.</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Si annulée, Poison</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R46" t="inlineStr" s="1">
@@ -4508,14 +4733,19 @@
       </c>
       <c r="S46" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">023.png</t>
+          <t xml:space="preserve">045.png</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/045.png</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">023*</t>
+          <t xml:space="preserve">046</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="1">
@@ -4535,67 +4765,67 @@
       </c>
       <c r="E47" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Alternative</t>
+          <t xml:space="preserve">Normale</t>
         </is>
       </c>
       <c r="F47" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Rare</t>
+          <t xml:space="preserve">Commune</t>
         </is>
       </c>
       <c r="G47" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">✶</t>
+          <t xml:space="preserve">●</t>
         </is>
       </c>
       <c r="H47" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Essaim</t>
+          <t xml:space="preserve">Ombre</t>
         </is>
       </c>
       <c r="I47" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Attaque</t>
+          <t xml:space="preserve">Contre</t>
         </is>
       </c>
       <c r="J47" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">🗡️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="K47" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#e5484d</t>
+          <t xml:space="preserve">#22b8cf</t>
         </is>
       </c>
       <c r="L47" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M47" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Vert</t>
+          <t xml:space="preserve">Noir</t>
         </is>
       </c>
       <c r="N47" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#43c46b</t>
+          <t xml:space="preserve">#6b6f80</t>
         </is>
       </c>
       <c r="O47" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Si annulée : Poison 2 (l’adversaire perd 1 PV à la fin de chacun des prochains duels).</t>
+          <t xml:space="preserve">Annule la carte d’en face, quelle qu’elle soit. Sacrifice 1 (tu perds ces PV, le bouclier ne les absorbe pas).</t>
         </is>
       </c>
       <c r="P47" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Le bourdonnement s’entend à trois planètes de distance.</t>
+          <t xml:space="preserve">Ce qui se cache dans l’ombre efface tout. Même ta meilleure carte.</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Si annulée, Poison</t>
+          <t xml:space="preserve">Sacrifice</t>
         </is>
       </c>
       <c r="R47" t="inlineStr" s="1">
@@ -4605,14 +4835,19 @@
       </c>
       <c r="S47" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">023-alt.png</t>
+          <t xml:space="preserve">046.png</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/046.png</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">024</t>
+          <t xml:space="preserve">047</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="1">
@@ -4647,7 +4882,7 @@
       </c>
       <c r="H48" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Floraison</t>
+          <t xml:space="preserve">Trou noir</t>
         </is>
       </c>
       <c r="I48" t="inlineStr" s="1">
@@ -4672,27 +4907,27 @@
       </c>
       <c r="M48" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Vert</t>
+          <t xml:space="preserve">Noir</t>
         </is>
       </c>
       <c r="N48" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#43c46b</t>
+          <t xml:space="preserve">#6b6f80</t>
         </is>
       </c>
       <c r="O48" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Soigne 1 PV par carte Verte que tu as déjà révélée ce tour.</t>
+          <t xml:space="preserve">Annule la carte d’en face et la détruit. Usage unique (défaussée après usage).</t>
         </is>
       </c>
       <c r="P48" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Au printemps de Spore, tout repousse. Même les blessures.</t>
+          <t xml:space="preserve">Ce qui entre n’en ressort jamais.</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Détruire, Usage unique</t>
         </is>
       </c>
       <c r="R48" t="inlineStr" s="1">
@@ -4702,14 +4937,19 @@
       </c>
       <c r="S48" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">024.png</t>
+          <t xml:space="preserve">047.png</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/047.png</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">024*</t>
+          <t xml:space="preserve">048</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="1">
@@ -4729,69 +4969,69 @@
       </c>
       <c r="E49" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Alternative</t>
+          <t xml:space="preserve">Normale</t>
         </is>
       </c>
       <c r="F49" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Rare</t>
+          <t xml:space="preserve">Commune</t>
         </is>
       </c>
       <c r="G49" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">✶</t>
+          <t xml:space="preserve">●</t>
         </is>
       </c>
       <c r="H49" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Floraison</t>
+          <t xml:space="preserve">Âme sombre</t>
         </is>
       </c>
       <c r="I49" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Tactique</t>
+          <t xml:space="preserve">Attaque</t>
         </is>
       </c>
       <c r="J49" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">✨</t>
+          <t xml:space="preserve">🗡️</t>
         </is>
       </c>
       <c r="K49" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">#9b6dff</t>
+          <t xml:space="preserve">#e5484d</t>
         </is>
       </c>
       <c r="L49" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Noir</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">#6b6f80</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">+1 par Sacrifice (tu perds ces PV, le bouclier ne les absorbe pas) que tu as fait ce tour.</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Plus tu souffres, plus elle grandit.</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="M49" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Vert</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#43c46b</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Soigne 1 PV par carte Verte que tu as déjà révélée ce tour.</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Les fleurs de Spore chantent. Faux, mais avec cœur.</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="R49" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Tylt</t>
@@ -4799,4663 +5039,12 @@
       </c>
       <c r="S49" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">024-alt.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">025</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Normale</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Commune</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">●</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Bouclier solaire</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Garde</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">🛡️</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#d4a017</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Jaune</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#f5c02e</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Le soleil protège ceux qui savent l’attendre.</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">025.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">025*</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Alternative</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Commune</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">●</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Bouclier solaire</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Garde</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">🛡️</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#d4a017</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Jaune</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#f5c02e</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Un lever de soleil sur un bouclier. Rien de plus beau.</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">025-alt.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">026</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Normale</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Peu commune</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✦</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Rempart</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Garde</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">🛡️</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#d4a017</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Jaune</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#f5c02e</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Le bouclier n’arrive qu’après les dégâts de ce duel.</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Lent à monter. Impossible à faire tomber.</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">026.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">026*</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Alternative</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Peu commune</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✦</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Rempart</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Garde</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">🛡️</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#d4a017</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Jaune</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#f5c02e</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Le bouclier n’arrive qu’après les dégâts de ce duel.</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Il a fallu mille ans pour le construire, et une seconde pour le regretter de l’autre côté.</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">026-alt.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">027</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Normale</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Commune</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">●</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Épines dorées</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Garde</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">🛡️</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#d4a017</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Jaune</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#f5c02e</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Épines 2 : si une Attaque adverse te touche pendant ce duel, son attaquant subit 2 dégâts.</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Touche-moi si tu l’oses. Vraiment, ose.</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Épines</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">027.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">027*</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Alternative</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Commune</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">●</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Épines dorées</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Garde</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">🛡️</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#d4a017</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Jaune</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#f5c02e</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Épines 2 : si une Attaque adverse te touche pendant ce duel, son attaquant subit 2 dégâts.</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Jolie, dorée et piquante. Ne pas caresser.</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Épines</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">027-alt.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">028</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Normale</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Rare</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✶</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Bouclier galactique</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Garde</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">🛡️</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#d4a017</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Jaune</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#f5c02e</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Ton bouclier ne disparaît pas à la fin du tour.</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Le Bouclier tient depuis mille ans. Il tiendra bien un tour de plus.</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">028.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">028*</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Alternative</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Rare</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✶</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Bouclier galactique</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Garde</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">🛡️</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#d4a017</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Jaune</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#f5c02e</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Ton bouclier ne disparaît pas à la fin du tour.</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Sa lumière se voit depuis l’autre bout de la galaxie.</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">028-alt.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">029</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Normale</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Commune</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">●</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Éclat solaire</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Attaque</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">🗡️</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#e5484d</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">X</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Jaune</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#f5c02e</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">X = ton bouclier actuel (6 au plus). Le bouclier n’est pas dépensé.</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Toute la lumière qu’il a gardée, il te la renvoie d’un coup.</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">029.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">029*</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Alternative</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Commune</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">●</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Éclat solaire</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Attaque</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">🗡️</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#e5484d</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">X</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Jaune</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#f5c02e</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">X = ton bouclier actuel (6 au plus). Le bouclier n’est pas dépensé.</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Il a stocké le soleil tout l’été pour ce moment.</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">029-alt.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">030</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Normale</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Rare</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✶</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Bénédiction</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tactique</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✨</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#9b6dff</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Jaune</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#f5c02e</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Double ton bouclier (10 au plus).</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Deux fois plus de lumière, deux fois plus de soucis pour toi.</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">030.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">030*</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Alternative</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Rare</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✶</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Bénédiction</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tactique</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✨</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#9b6dff</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Jaune</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#f5c02e</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Double ton bouclier (10 au plus).</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Les anciens disent qu’elle porte bonheur. Aux autres, pas à toi.</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">030-alt.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">031</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Normale</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Commune</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">●</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Garde galactique</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Contre</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">🌀</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#22b8cf</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Jaune</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#f5c02e</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Annule une Attaque ; si c’est le cas, gagne 2 de bouclier.</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Halte ! Plus personne ne passe.</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S62" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">031.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">031*</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Alternative</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Commune</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">●</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Garde galactique</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Contre</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">🌀</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#22b8cf</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Jaune</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#f5c02e</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Annule une Attaque ; si c’est le cas, gagne 2 de bouclier.</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Il n’a pas bougé depuis cent ans. Ce n’est pas aujourd’hui qu’il va bouger.</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">031-alt.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">032</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Normale</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Peu commune</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✦</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Aveuglement</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tactique</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✨</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#9b6dff</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Jaune</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#f5c02e</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">La prochaine Attaque adverse fait −3.</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Attention à la tête… et surtout aux yeux.</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S64" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">032.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">032*</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Alternative</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Peu commune</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✦</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Aveuglement</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tactique</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✨</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#9b6dff</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Jaune</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#f5c02e</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">La prochaine Attaque adverse fait −3.</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Attention à la tête… et prévois des lunettes de soleil.</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S65" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">032-alt.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">033</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Normale</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Rare</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✶</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Télépathie</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tactique</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✨</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#9b6dff</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Violet</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#a35cff</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Vision 2 (regarde les prochaines cartes de la pile adverse), puis tu peux échanger tes 2 prochaines cartes.</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Jimmy sait ce que tu vas jouer. Jimmy sait tout.</t>
-        </is>
-      </c>
-      <c r="Q66" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Vision, Échange</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S66" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">033.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">033*</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Alternative</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Rare</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✶</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Télépathie</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tactique</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✨</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#9b6dff</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Violet</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#a35cff</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Vision 2 (regarde les prochaines cartes de la pile adverse), puis tu peux échanger tes 2 prochaines cartes.</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Jimmy lit dans tes pensées. Elles sont… intéressantes.</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Vision, Échange</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S67" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">033-alt.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">034</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Normale</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Peu commune</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✦</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tour de passe-passe</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tactique</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✨</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#9b6dff</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Violet</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#a35cff</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Échange les 2 prochaines cartes de l’adversaire, puis Vision 2 (regarde les prochaines cartes de la pile adverse).</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tu étais sûr de l’ordre de tes cartes ? Tu l’étais.</t>
-        </is>
-      </c>
-      <c r="Q68" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Échange, Vision</t>
-        </is>
-      </c>
-      <c r="R68" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S68" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">034.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">034*</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Alternative</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Peu commune</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✦</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tour de passe-passe</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tactique</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✨</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#9b6dff</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Violet</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#a35cff</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Échange les 2 prochaines cartes de l’adversaire, puis Vision 2 (regarde les prochaines cartes de la pile adverse).</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Abracadabra. Tes plans ont disparu.</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Échange, Vision</t>
-        </is>
-      </c>
-      <c r="R69" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S69" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">034-alt.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">035</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Normale</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Commune</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">●</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Rayon néon</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Attaque</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">🗡️</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#e5484d</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Violet</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#a35cff</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">+2 si tu avais vu cette carte adverse grâce à une Vision (regarde les prochaines cartes de la pile adverse).</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Il t’a vu venir. De très loin.</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R70" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S70" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">035.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">035*</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Alternative</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Commune</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">●</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Rayon néon</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Attaque</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">🗡️</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#e5484d</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Violet</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#a35cff</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">+2 si tu avais vu cette carte adverse grâce à une Vision (regarde les prochaines cartes de la pile adverse).</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Il brille dans le noir. Et toi, tu n’y vois plus rien.</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S71" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">035-alt.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">036</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Normale</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Peu commune</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✦</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Mirage</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Contre</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">🌀</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#22b8cf</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Violet</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#a35cff</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Annule une Attaque ou une Tactique.</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tu frappes… du vide.</t>
-        </is>
-      </c>
-      <c r="Q72" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R72" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S72" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">036.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">036*</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Alternative</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Peu commune</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✦</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Mirage</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Contre</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">🌀</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#22b8cf</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Violet</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#a35cff</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Annule une Attaque ou une Tactique.</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tu es sûr d’avoir frappé quelque chose ?</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S73" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">036-alt.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">037</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Normale</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Rare</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✶</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Copie</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tactique</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✨</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#9b6dff</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Violet</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#a35cff</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Devient une copie de la carte d’en face.</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Ce que tu fais, je le fais. En mieux.</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S74" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">037.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">037*</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Alternative</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Rare</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✶</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Copie</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tactique</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✨</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#9b6dff</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Violet</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#a35cff</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Devient une copie de la carte d’en face.</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Il y a deux cartes identiques. L’une d’elles ment.</t>
-        </is>
-      </c>
-      <c r="Q75" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S75" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">037-alt.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">038</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Normale</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Commune</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">●</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Chaos</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Attaque</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">🗡️</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#e5484d</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Violet</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#a35cff</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Inverse l’ordre des 3 prochaines cartes de l’adversaire.</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tout ce que tu avais prévu ? À l’envers.</t>
-        </is>
-      </c>
-      <c r="Q76" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S76" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">038.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">038*</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Alternative</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Commune</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">●</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Chaos</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Attaque</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">🗡️</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#e5484d</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Violet</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#a35cff</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Inverse l’ordre des 3 prochaines cartes de l’adversaire.</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Haut, bas, gauche, droite : plus rien ne veut rien dire.</t>
-        </is>
-      </c>
-      <c r="Q77" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R77" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S77" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">038-alt.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">039</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Normale</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Commune</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">●</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Rayon miroir</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Attaque</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">🗡️</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#e5484d</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Violet</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#a35cff</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">+2 si la carte d’en face est une Tactique.</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Les ruses se retournent toujours contre leur auteur.</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R78" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S78" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">039.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">039*</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Alternative</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Commune</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">●</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Rayon miroir</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Attaque</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">🗡️</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#e5484d</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Violet</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#a35cff</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">+2 si la carte d’en face est une Tactique.</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Ta ruse t’a fait un clin d’œil, puis elle t’a frappé.</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R79" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S79" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">039-alt.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">040</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Normale</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Commune</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">●</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Déjà-vu</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tactique</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✨</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#9b6dff</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Violet</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#a35cff</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Devient une copie de ta carte précédente.</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tu as l’impression d’avoir déjà vu cette carte ? Normal.</t>
-        </is>
-      </c>
-      <c r="Q80" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R80" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S80" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">040.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">040*</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Alternative</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Commune</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">●</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Déjà-vu</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tactique</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✨</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#9b6dff</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Violet</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#a35cff</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Devient une copie de ta carte précédente.</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Cette phrase, tu l’as déjà lue. Ou pas ?</t>
-        </is>
-      </c>
-      <c r="Q81" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R81" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S81" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">040-alt.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">041</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Normale</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Commune</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">●</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Lame des abysses</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Attaque</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">🗡️</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#e5484d</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Noir</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#6b6f80</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Perforant (ignore le bouclier). Sacrifice 1 (tu perds ces PV, le bouclier ne les absorbe pas).</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Chaque coup se paie. Celui-là en vaut la peine.</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Perforant, Sacrifice</t>
-        </is>
-      </c>
-      <c r="R82" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S82" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">041.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">041*</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Alternative</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Commune</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">●</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Lame des abysses</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Attaque</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">🗡️</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#e5484d</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Noir</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#6b6f80</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Perforant (ignore le bouclier). Sacrifice 1 (tu perds ces PV, le bouclier ne les absorbe pas).</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Forgée au fond des abysses, là où même la lumière a peur.</t>
-        </is>
-      </c>
-      <c r="Q83" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Perforant, Sacrifice</t>
-        </is>
-      </c>
-      <c r="R83" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S83" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">041-alt.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">042</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Normale</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Commune</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">●</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Brise-bouclier</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tactique</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✨</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#9b6dff</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Noir</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#6b6f80</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Détruit tout le bouclier adverse.</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Plus de bouclier. Plus d’excuses.</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R84" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S84" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">042.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">042*</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Alternative</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Commune</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">●</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Brise-bouclier</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tactique</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✨</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#9b6dff</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Noir</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#6b6f80</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Détruit tout le bouclier adverse.</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Il frappe, et ton bouclier n’est plus qu’un souvenir.</t>
-        </is>
-      </c>
-      <c r="Q85" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R85" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S85" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">042-alt.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">043</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Normale</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Peu commune</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✦</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Malédiction</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tactique</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✨</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#9b6dff</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Noir</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#6b6f80</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">L’adversaire ne gagne ni bouclier ni PV pendant les 3 duels suivants.</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Les abysses n’oublient jamais un affront.</t>
-        </is>
-      </c>
-      <c r="Q86" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R86" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S86" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">043.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">043*</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Alternative</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Peu commune</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✦</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Malédiction</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tactique</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✨</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#9b6dff</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Noir</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#6b6f80</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">L’adversaire ne gagne ni bouclier ni PV pendant les 3 duels suivants.</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tu entends ce murmure ? C’est ton bouclier qui s’en va.</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S87" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">043-alt.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">044</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Normale</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Peu commune</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✦</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Pacte</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tactique</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✨</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#9b6dff</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Noir</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#6b6f80</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Sacrifice 2 (tu perds ces PV, le bouclier ne les absorbe pas). Préparation : ta prochaine Attaque fait le double.</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Un peu de toi pour beaucoup de moi.</t>
-        </is>
-      </c>
-      <c r="Q88" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Sacrifice, Préparation</t>
-        </is>
-      </c>
-      <c r="R88" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S88" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">044.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">044*</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Alternative</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Peu commune</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✦</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Pacte</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tactique</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✨</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#9b6dff</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Noir</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#6b6f80</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Sacrifice 2 (tu perds ces PV, le bouclier ne les absorbe pas). Préparation : ta prochaine Attaque fait le double.</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Signe ici. Et ici. Et là aussi. Avec ton sang, bien sûr.</t>
-        </is>
-      </c>
-      <c r="Q89" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Sacrifice, Préparation</t>
-        </is>
-      </c>
-      <c r="R89" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S89" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">044-alt.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">045</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Normale</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Rare</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✶</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Exécution</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Attaque</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">🗡️</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#e5484d</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Noir</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#6b6f80</t>
-        </is>
-      </c>
-      <c r="O90" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Fait 8 si l’adversaire a 8 PV ou moins.</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Quand la fin approche, elle frappe plus fort.</t>
-        </is>
-      </c>
-      <c r="Q90" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R90" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S90" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">045.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">045*</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Alternative</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Rare</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✶</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Exécution</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Attaque</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">🗡️</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#e5484d</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Noir</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#6b6f80</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Fait 8 si l’adversaire a 8 PV ou moins.</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Le dernier visage que voient les champions fatigués.</t>
-        </is>
-      </c>
-      <c r="Q91" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R91" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S91" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">045-alt.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">046</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Normale</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Commune</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">●</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Ombre</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Contre</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">🌀</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#22b8cf</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Noir</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#6b6f80</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Annule la carte d’en face, quelle qu’elle soit. Sacrifice 1 (tu perds ces PV, le bouclier ne les absorbe pas).</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Ce qui se cache dans l’ombre efface tout. Même ta meilleure carte.</t>
-        </is>
-      </c>
-      <c r="Q92" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Sacrifice</t>
-        </is>
-      </c>
-      <c r="R92" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S92" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">046.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">046*</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Alternative</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Commune</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">●</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Ombre</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Contre</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">🌀</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#22b8cf</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Noir</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#6b6f80</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Annule la carte d’en face, quelle qu’elle soit. Sacrifice 1 (tu perds ces PV, le bouclier ne les absorbe pas).</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tu crois être seul ? Regarde derrière toi.</t>
-        </is>
-      </c>
-      <c r="Q93" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Sacrifice</t>
-        </is>
-      </c>
-      <c r="R93" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S93" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">046-alt.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">047</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Normale</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Rare</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✶</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Trou noir</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tactique</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✨</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#9b6dff</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Noir</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#6b6f80</t>
-        </is>
-      </c>
-      <c r="O94" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Annule la carte d’en face et la détruit. Usage unique (défaussée après usage).</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Ce qui entre n’en ressort jamais.</t>
-        </is>
-      </c>
-      <c r="Q94" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Détruire, Usage unique</t>
-        </is>
-      </c>
-      <c r="R94" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S94" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">047.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">047*</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Alternative</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Rare</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✶</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Trou noir</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tactique</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">✨</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#9b6dff</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Noir</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#6b6f80</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Annule la carte d’en face et la détruit. Usage unique (défaussée après usage).</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Il a avalé une flotte entière. Il a encore un peu faim.</t>
-        </is>
-      </c>
-      <c r="Q95" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Détruire, Usage unique</t>
-        </is>
-      </c>
-      <c r="R95" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S95" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">047-alt.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Normale</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Commune</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">●</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Âme sombre</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Attaque</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">🗡️</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#e5484d</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Noir</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#6b6f80</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">+1 par Sacrifice (tu perds ces PV, le bouclier ne les absorbe pas) que tu as fait ce tour.</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Plus tu souffres, plus elle grandit.</t>
-        </is>
-      </c>
-      <c r="Q96" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R96" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S96" t="inlineStr" s="1">
-        <is>
           <t xml:space="preserve">048.png</t>
         </is>
       </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048*</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Premier Contact</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">PCO</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Alternative</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Commune</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">●</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Âme sombre</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Attaque</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">🗡️</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#e5484d</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Noir</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">#6b6f80</t>
-        </is>
-      </c>
-      <c r="O97" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">+1 par Sacrifice (tu perds ces PV, le bouclier ne les absorbe pas) que tu as fait ce tour.</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Elle se nourrit de chaque sacrifice. Elle n’est jamais rassasiée.</t>
-        </is>
-      </c>
-      <c r="Q97" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R97" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tylt</t>
-        </is>
-      </c>
-      <c r="S97" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">048-alt.png</t>
+      <c r="T49" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/048.png</t>
         </is>
       </c>
     </row>
@@ -9562,6 +5151,11 @@
           <t xml:space="preserve">Fichier_image</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Image</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr" s="1">
@@ -9659,6 +5253,11 @@
           <t xml:space="preserve">C01.png</t>
         </is>
       </c>
+      <c r="T2" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/C01.png</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr" s="1">
@@ -9756,6 +5355,11 @@
           <t xml:space="preserve">C01-alt.png</t>
         </is>
       </c>
+      <c r="T3" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/C01-alt.png</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr" s="1">
@@ -9853,6 +5457,11 @@
           <t xml:space="preserve">C02.png</t>
         </is>
       </c>
+      <c r="T4" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/C02.png</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr" s="1">
@@ -9950,6 +5559,11 @@
           <t xml:space="preserve">C02-alt.png</t>
         </is>
       </c>
+      <c r="T5" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/C02-alt.png</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr" s="1">
@@ -10047,6 +5661,11 @@
           <t xml:space="preserve">C03.png</t>
         </is>
       </c>
+      <c r="T6" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/C03.png</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr" s="1">
@@ -10144,6 +5763,11 @@
           <t xml:space="preserve">C03-alt.png</t>
         </is>
       </c>
+      <c r="T7" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/C03-alt.png</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr" s="1">
@@ -10241,6 +5865,11 @@
           <t xml:space="preserve">C04.png</t>
         </is>
       </c>
+      <c r="T8" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/C04.png</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr" s="1">
@@ -10338,6 +5967,11 @@
           <t xml:space="preserve">C04-alt.png</t>
         </is>
       </c>
+      <c r="T9" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/C04-alt.png</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr" s="1">
@@ -10435,6 +6069,11 @@
           <t xml:space="preserve">C05.png</t>
         </is>
       </c>
+      <c r="T10" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/C05.png</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr" s="1">
@@ -10532,6 +6171,11 @@
           <t xml:space="preserve">C05-alt.png</t>
         </is>
       </c>
+      <c r="T11" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/C05-alt.png</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr" s="1">
@@ -10629,6 +6273,11 @@
           <t xml:space="preserve">C06.png</t>
         </is>
       </c>
+      <c r="T12" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/C06.png</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr" s="1">
@@ -10726,6 +6375,11 @@
           <t xml:space="preserve">C06-alt.png</t>
         </is>
       </c>
+      <c r="T13" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/C06-alt.png</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr" s="1">
@@ -10823,6 +6477,11 @@
           <t xml:space="preserve">C07.png</t>
         </is>
       </c>
+      <c r="T14" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/C07.png</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr" s="1">
@@ -10920,6 +6579,11 @@
           <t xml:space="preserve">C07-alt.png</t>
         </is>
       </c>
+      <c r="T15" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/C07-alt.png</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr" s="1">
@@ -11017,6 +6681,11 @@
           <t xml:space="preserve">C08.png</t>
         </is>
       </c>
+      <c r="T16" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/C08.png</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr" s="1">
@@ -11114,6 +6783,11 @@
           <t xml:space="preserve">C08-alt.png</t>
         </is>
       </c>
+      <c r="T17" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/C08-alt.png</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr" s="1">
@@ -11211,6 +6885,11 @@
           <t xml:space="preserve">C09.png</t>
         </is>
       </c>
+      <c r="T18" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/C09.png</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr" s="1">
@@ -11308,6 +6987,11 @@
           <t xml:space="preserve">C09-alt.png</t>
         </is>
       </c>
+      <c r="T19" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/C09-alt.png</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr" s="1">
@@ -11405,6 +7089,11 @@
           <t xml:space="preserve">C10.png</t>
         </is>
       </c>
+      <c r="T20" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/C10.png</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr" s="1">
@@ -11502,6 +7191,11 @@
           <t xml:space="preserve">C10-alt.png</t>
         </is>
       </c>
+      <c r="T21" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/C10-alt.png</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr" s="1">
@@ -11599,6 +7293,11 @@
           <t xml:space="preserve">C11.png</t>
         </is>
       </c>
+      <c r="T22" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/C11.png</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr" s="1">
@@ -11696,6 +7395,11 @@
           <t xml:space="preserve">C11-alt.png</t>
         </is>
       </c>
+      <c r="T23" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/C11-alt.png</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr" s="1">
@@ -11793,6 +7497,11 @@
           <t xml:space="preserve">C12.png</t>
         </is>
       </c>
+      <c r="T24" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/C12.png</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr" s="1">
@@ -11890,6 +7599,11 @@
           <t xml:space="preserve">C12-alt.png</t>
         </is>
       </c>
+      <c r="T25" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/C12-alt.png</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr" s="1">
@@ -11987,6 +7701,11 @@
           <t xml:space="preserve">C13.png</t>
         </is>
       </c>
+      <c r="T26" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/C13.png</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr" s="1">
@@ -12084,6 +7803,11 @@
           <t xml:space="preserve">C13-alt.png</t>
         </is>
       </c>
+      <c r="T27" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/C13-alt.png</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr" s="1">
@@ -12181,6 +7905,11 @@
           <t xml:space="preserve">C14.png</t>
         </is>
       </c>
+      <c r="T28" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/C14.png</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr" s="1">
@@ -12278,6 +8007,11 @@
           <t xml:space="preserve">C14-alt.png</t>
         </is>
       </c>
+      <c r="T29" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/C14-alt.png</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr" s="1">
@@ -12375,6 +8109,11 @@
           <t xml:space="preserve">C15.png</t>
         </is>
       </c>
+      <c r="T30" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/C15.png</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr" s="1">
@@ -12470,6 +8209,11 @@
       <c r="S31" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">C15-alt.png</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/C15-alt.png</t>
         </is>
       </c>
     </row>
@@ -12551,6 +8295,11 @@
           <t xml:space="preserve">Fichier_image</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Image</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr" s="1">
@@ -12623,6 +8372,11 @@
           <t xml:space="preserve">M01.png</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/M01.png</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr" s="1">
@@ -12695,6 +8449,11 @@
           <t xml:space="preserve">M01-alt.png</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/M01-alt.png</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr" s="1">
@@ -12767,6 +8526,11 @@
           <t xml:space="preserve">M02.png</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/M02.png</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr" s="1">
@@ -12839,6 +8603,11 @@
           <t xml:space="preserve">M02-alt.png</t>
         </is>
       </c>
+      <c r="O5" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/M02-alt.png</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr" s="1">
@@ -12911,6 +8680,11 @@
           <t xml:space="preserve">M03.png</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/M03.png</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr" s="1">
@@ -12983,6 +8757,11 @@
           <t xml:space="preserve">M03-alt.png</t>
         </is>
       </c>
+      <c r="O7" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/M03-alt.png</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr" s="1">
@@ -13055,6 +8834,11 @@
           <t xml:space="preserve">M04.png</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/M04.png</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr" s="1">
@@ -13127,6 +8911,11 @@
           <t xml:space="preserve">M04-alt.png</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/M04-alt.png</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr" s="1">
@@ -13199,6 +8988,11 @@
           <t xml:space="preserve">M05.png</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/M05.png</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr" s="1">
@@ -13271,6 +9065,11 @@
           <t xml:space="preserve">M05-alt.png</t>
         </is>
       </c>
+      <c r="O11" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/M05-alt.png</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr" s="1">
@@ -13343,6 +9142,11 @@
           <t xml:space="preserve">M06.png</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/M06.png</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr" s="1">
@@ -13413,6 +9217,11 @@
       <c r="N13" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">M06-alt.png</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">https://img.neutron-games.net/image_tcg/M06-alt.png</t>
         </is>
       </c>
     </row>
